--- a/event_registration_forms/027_workshop_accessibility_and_allergy_survey--event_registration_forms.xlsx
+++ b/event_registration_forms/027_workshop_accessibility_and_allergy_survey--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'wheelchair_accessible',_'value':_'wheelchair_accessible'}</t>
+          <t>wheelchair_accessible</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Wheelchair accessible', 'value': 'Wheelchair accessible'}</t>
+          <t>Wheelchair accessible</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'service_animal_accessible',_'value':_'service_animal_accessible'}</t>
+          <t>service_animal_accessible</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Service animal accessible', 'value': 'Service animal accessible'}</t>
+          <t>Service animal accessible</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'sign_language_accessible',_'value':_'sign_language_accessible'}</t>
+          <t>sign_language_accessible</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Sign language accessible', 'value': 'Sign language accessible'}</t>
+          <t>Sign language accessible</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'peanut',_'value':_'peanut'}</t>
+          <t>peanut</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Peanut', 'value': 'Peanut'}</t>
+          <t>Peanut</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'milk',_'value':_'milk'}</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Milk', 'value': 'Milk'}</t>
+          <t>Milk</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'egg',_'value':_'egg'}</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Egg', 'value': 'Egg'}</t>
+          <t>Egg</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'fish',_'value':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Fish', 'value': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'shellfish',_'value':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Shellfish', 'value': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'crustacean',_'value':_'crustacean'}</t>
+          <t>crustacean</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Crustacean', 'value': 'Crustacean'}</t>
+          <t>Crustacean</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'sesame',_'value':_'sesame'}</t>
+          <t>sesame</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Sesame', 'value': 'Sesame'}</t>
+          <t>Sesame</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'soy',_'value':_'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Soy', 'value': 'Soy'}</t>
+          <t>Soy</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'tree_nut',_'value':_'tree_nut'}</t>
+          <t>tree_nut</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Tree nut', 'value': 'Tree nut'}</t>
+          <t>Tree nut</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'wheat',_'value':_'wheat'}</t>
+          <t>wheat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Wheat', 'value': 'Wheat'}</t>
+          <t>Wheat</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'cottonseed',_'value':_'cottonseed'}</t>
+          <t>cottonseed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Cottonseed', 'value': 'Cottonseed'}</t>
+          <t>Cottonseed</t>
         </is>
       </c>
     </row>
@@ -1041,148 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'options':_[],_'label':_'sesame',_'value':_'sesame'}</t>
+          <t>mollusks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'options': [], 'label': 'Sesame', 'value': 'Sesame'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'mollusks',_'value':_'mollusks'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Mollusks', 'value': 'Mollusks'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'egg',_'value':_'egg'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Egg', 'value': 'Egg'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'sesame',_'value':_'sesame'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Sesame', 'value': 'Sesame'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'fish',_'value':_'fish'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Fish', 'value': 'Fish'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'crustacean',_'value':_'crustacean'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Crustacean', 'value': 'Crustacean'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'crustacean',_'value':_'crustacean'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Crustacean', 'value': 'Crustacean'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'fish',_'value':_'fish'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Fish', 'value': 'Fish'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>workshop_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'options':_[],_'label':_'sesame',_'value':_'sesame'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'options': [], 'label': 'Sesame', 'value': 'Sesame'}</t>
+          <t>Mollusks</t>
         </is>
       </c>
     </row>
